--- a/InputFiles/CDS/Kidsfirst basecounts.xlsx
+++ b/InputFiles/CDS/Kidsfirst basecounts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sofia\CRDC_CLI\TestData QA Env\GC March release\KidsFirst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davids3\CRDC_CLI\GC_2026_Sof\Commons_Automation\InputFiles\CDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70E312B-EF0D-43ED-B36C-2CEB700F098E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71290A04-2AF2-4AFC-90F6-4313DB54D6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE9600E8-8B49-4E01-9C55-74577F082F21}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>PHS Accession</t>
   </si>
@@ -81,13 +81,31 @@
   </si>
   <si>
     <t>Kids First Pediatric Research Study in Familial Predisposition to Hematopoietic Malignancies</t>
+  </si>
+  <si>
+    <t>phs002322</t>
+  </si>
+  <si>
+    <t>First: Genetic Predisposition to Intracranial Germ Cell Tumors</t>
+  </si>
+  <si>
+    <t>phs003215</t>
+  </si>
+  <si>
+    <t>Texas Pediatric Patient Derived Xenograft</t>
+  </si>
+  <si>
+    <t>phs001878</t>
+  </si>
+  <si>
+    <t>Gabriella Miller Kids First Pediatric Research Program in Novel Cancer Susceptibility in Families (from BASIC3)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +139,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF004C73"/>
+      <name val="Nunito"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -130,7 +153,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -153,12 +176,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -178,6 +212,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -513,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1371AD0-9167-4557-AAE2-5A83EA1DE8C4}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.81640625" customWidth="1"/>
@@ -624,6 +663,57 @@
         <v>4728</v>
       </c>
     </row>
+    <row r="7" spans="1:5" ht="24" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="6">
+        <v>356</v>
+      </c>
+      <c r="D7" s="6">
+        <v>358</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="10">
+        <v>51</v>
+      </c>
+      <c r="D8" s="10">
+        <v>362</v>
+      </c>
+      <c r="E8" s="11">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6">
+        <v>611</v>
+      </c>
+      <c r="D9" s="6">
+        <v>276</v>
+      </c>
+      <c r="E9" s="4">
+        <v>7353</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" location="/study/phs001228" display="https://general-qa.datacommons.cancer.gov/ - /study/phs001228" xr:uid="{D912CE8A-C79F-411A-B633-9AD3F278839D}"/>
@@ -631,6 +721,8 @@
     <hyperlink ref="A4" r:id="rId3" location="/study/phs002187" display="https://general-qa.datacommons.cancer.gov/ - /study/phs002187" xr:uid="{D42C061C-6165-4CF7-B8D5-90DD145940CC}"/>
     <hyperlink ref="A5" r:id="rId4" location="/study/phs001714" display="https://general-qa.datacommons.cancer.gov/ - /study/phs001714" xr:uid="{EE852FB1-3B94-4452-813F-5885C1BDCFBB}"/>
     <hyperlink ref="A6" r:id="rId5" location="/study/phs001738" display="https://general-qa.datacommons.cancer.gov/ - /study/phs001738" xr:uid="{4420DDF5-A9A1-4308-8961-2818CAE8B0C0}"/>
+    <hyperlink ref="A7" r:id="rId6" location="/study/phs002322" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs002322" xr:uid="{761D2B61-0294-453A-9E87-596EEBBB1019}"/>
+    <hyperlink ref="A9" r:id="rId7" location="/study/phs001878" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs001878" xr:uid="{FDD2A209-F1F4-44D2-A53B-3F76D7A98BAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/InputFiles/CDS/Kidsfirst basecounts.xlsx
+++ b/InputFiles/CDS/Kidsfirst basecounts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davids3\CRDC_CLI\GC_2026_Sof\Commons_Automation\InputFiles\CDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71290A04-2AF2-4AFC-90F6-4313DB54D6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E415E53A-8857-494F-97FF-C4A6795DF507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE9600E8-8B49-4E01-9C55-74577F082F21}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BE9600E8-8B49-4E01-9C55-74577F082F21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -105,7 +105,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,19 @@
     <font>
       <sz val="8"/>
       <color rgb="FF004C73"/>
+      <name val="Nunito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
       <name val="Nunito"/>
     </font>
   </fonts>
@@ -192,7 +205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -215,8 +228,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -578,7 +600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -595,7 +617,7 @@
         <v>49518</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -612,7 +634,7 @@
         <v>26788</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -629,7 +651,7 @@
         <v>3342</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -664,53 +686,53 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="24" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="10">
         <v>356</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="10">
         <v>358</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="11">
         <v>10667</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5" ht="24" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="12">
         <v>51</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <v>362</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="13">
         <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="10">
         <v>611</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="10">
         <v>276</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="11">
         <v>7353</v>
       </c>
     </row>
